--- a/docs/VESMA_podklad_pre_energetickeho_experta.xlsx
+++ b/docs/VESMA_podklad_pre_energetickeho_experta.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Úvod" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="1. Referenčné hodnoty" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Váhy porovnania" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3. Kotol na biomasu" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3. Kotol a palivá" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="4. Osvetlenie W na m2" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="5. Dennostupne" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
@@ -46,12 +46,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
+      <i val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -165,28 +165,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -605,126 +605,178 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ČO POTREBUJEME</t>
+          <t>ČO UŽ JE ROZHODNUTÉ — NA TO SA NEPÝTAME</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>V nástroji je päť miest, kde chýba číslo, ktoré nemá kto vymyslieť. Nevyplnili sme ich sami</t>
+          <t>Vaše pripomienky z augusta 2026 sú zapracované a späť ich neotvárame: FV potenciál sa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>zámerne: na výstupe nie je vidieť, že hodnota je odhad, a nástroj pre samosprávy by tým začal</t>
+          <t>počíta iba zo striech do 15° sklonu, parametre viazané na budovy prešli z počtu budov na</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>klamať sebavedomo. Radšej zostali prázdne.</t>
+          <t>vykurovanú plochu, pribudol prechod plyn → biomasa (uhlie ako cieľ nie), pri osvetlení je</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>presnejší počet svietidiel a plocha zostáva len ako záloha, a vypočítaná potreba</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Každý hárok je jedna tabuľka. Žlté bunky sú na vyplnenie, zelený riadok je vzor s formátom,</t>
+          <t>z energetického certifikátu sa nikde nemieša s nameranou spotrebou z faktúr.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>aký očakávame — prepíšte ho alebo zmažte. Ostatné bunky sú kontext, netreba ich meniť.</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>ČO POTREBUJEME</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Ak niektorú hodnotu neviete podložiť zdrojom, nechajte ju prázdnu a napíšte to do poznámky.</t>
+          <t>V nástroji je päť miest, kde chýba číslo, ktoré nemá kto vymyslieť. Nevyplnili sme ich sami</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>zámerne: na výstupe nie je vidieť, že hodnota je odhad, a nástroj pre samosprávy by tým začal</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>klamať sebavedomo. Radšej zostali prázdne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Každý hárok je jedna tabuľka. Žlté bunky sú na vyplnenie, zelený riadok je vzor s formátom,</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>aký očakávame — prepíšte ho alebo zmažte. Ostatné bunky sú kontext, netreba ich meniť.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Ak niektorú hodnotu neviete podložiť zdrojom, nechajte ju prázdnu a napíšte to do poznámky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>Prázdna hodnota je pre nás lepší výsledok než odhad, ktorý sa bude tváriť ako fakt.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>PREHĽAD HÁRKOV</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>1. Referenčné hodnoty — kWh/(m²·rok) podľa typu budovy. Najdôležitejšie — bez nich VESMA vie povedať, koľko budova spotrebuje, ale nie či je to veľa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2. Váhy porovnania — Váhy 13 parametrov, podľa ktorých sa zoraďujú areály. Máme návrh, potrebujeme potvrdenie alebo opravu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>3. Kotol na biomasu — Orientačná cena a návratnosť. Jediné opatrenie v katalógu, kde tieto údaje chýbajú.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>4. Osvetlenie W na m2 — Hustota inštalovaného príkonu podľa typu priestoru. Oficiálna prepočtová tabuľka v SR neexistuje.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>5. Dennostupne — Dennostupne podľa okresu pre klimatickú normalizáciu (STN 73 0550). Otázka zdroja dát, nie odhadu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Kódy [E1]–[E5] sú z interného registra docs/chybajuce-hodnoty.md, kde sledujeme stav každej hodnoty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>1. Referenčné hodnoty [E1] — kWh/(m²·rok) podľa typu budovy. Najdôležitejšie — bez nich VESMA vie povedať, koľko budova spotrebuje, ale nie či je to veľa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2. Váhy porovnania [E2] — Váhy 13 parametrov, podľa ktorých sa zoraďujú areály. Máme návrh, potrebujeme potvrdenie alebo opravu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>3. Kotol a palivá [E3] — Cena a návratnosť kotla na biomasu + výhrevnosti palív, ktoré má VESMA napevno v kóde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>4. Osvetlenie W na m2 [E4] — Hustota inštalovaného príkonu podľa typu priestoru. Oficiálna prepočtová tabuľka v SR neexistuje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>5. Dennostupne [E5] — Dennostupne podľa okresu pre klimatickú normalizáciu (STN 73 0550). Otázka zdroja dát, nie odhadu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>LEGENDA</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>žltá bunka = sem vpíšte hodnotu</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>zelený riadok = vzor s očakávaným formátom, prepíšte alebo zmažte</t>
         </is>
@@ -754,57 +806,57 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>1. Referenčné hodnoty spotreby energie [kWh/(m²·rok)]</t>
+          <t>1. Referenčné hodnoty spotreby energie [kWh/(m²·rok)]  [E1]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Načo to je: VESMA počíta mernú spotrebu budovy z faktúr a vykurovanej plochy. Bez referenčnej</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>hodnoty ale nevie povedať, či je výsledok dobrý alebo zlý — vypíše len číslo bez kontextu.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Kvôli tomuto chýbajúcemu údaju je v porovnaní areálov dodnes vynechaný celý jeden parameter</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>(„Spotreba energie nad referenčnou hodnotou").</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr"/>
+      <c r="A6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Prosíme o hodnotu pre vykurovanie a zvlášť pre elektrinu — VESMA ich vedie oddelene, lebo</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>pole „spotreba elektriny" môže zahŕňať aj elektrinu na vykurovanie a súčet by ju počítal dvakrát.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Ak pre niektorý typ budovy referenčná hodnota nedáva zmysel, nechajte prázdne.</t>
         </is>
@@ -1169,60 +1221,60 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2. Váhy energetických parametrov pre porovnanie areálov</t>
+          <t>2. Váhy energetických parametrov pre porovnanie areálov  [E2]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Načo to je: keď má samospráva viac areálov, VESMA ich zoradí podľa toho, kde je najväčší</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>nevyužitý potenciál. Váhy rozhodujú o poradí, teda o tom, kam pôjdu peniaze.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr"/>
+      <c r="A4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Kladná váha = existujúci nevyužitý potenciál (problém na riešenie).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Záporná váha = existujúce opatrenie, ktoré potenciál znižuje.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Hodnota parametra sa vynásobí váhou a spočíta cez všetky parametre.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Stĺpec „návrh" sú hodnoty, ktoré sú v nástroji teraz. Vznikli z Vašich pripomienok z augusta 2026,</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ale nie sú potvrdené. Do stĺpca „potvrdená váha" vpíšte buď to isté číslo, alebo opravu.</t>
         </is>
@@ -1566,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1578,243 +1630,342 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3. Kotol na biomasu — cena a návratnosť</t>
+          <t>3. Kotol na biomasu a výhrevnosti palív  [E3]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Načo to je: VESMA má katalóg opatrení a pri každom uvádza orientačnú cenu a návratnosť.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Kotol na biomasu je jediné opatrenie, kde tieto údaje nemáme podložené — parameter vznikol</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>na Vašu pripomienku (prechod plyn → pelety/štiepka) a čísla nižšie sú náš hrubý odhad,</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>v aplikácii označený textom „hodnotu potvrdí energetický expert".</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr"/>
+      <c r="A6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Pre porovnanie sú pod tabuľkou uvedené hodnoty iných opatrení v katalógu, aby bolo vidieť,</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Druhá tabuľka je o výhrevnostiach. Tie v aplikácii NIE SÚ prázdne — sú napevno v kóde</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>v akej podrobnosti ich uvádzame.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>(src/data/constants.ts) a VESMA nimi prepočítava zadané kilogramy paliva na kWh. Nemáme</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>k nim ale zdroj a používateľ ich nevie prepísať, hoci bod 3 písm. a) prílohy č. 1 vyhlášky</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>č. 179/2015 Z. z. žiada výhrevnosť zistenú z dokladov. Preto ich dávame na kontrolu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Údaj</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Náš odhad (v aplikácii teraz)</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Potvrdená hodnota</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Poznámka</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>(vzor) Životnosť</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>neuvádzame</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>15 – 20 rokov</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>podľa typu horáka</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Orientačná cena</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>10 000 – 40 000 EUR podľa výkonu a riešenia skladu paliva</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Návratnosť</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>7 – 15 rokov</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Výhrevnosť peliet</t>
+          <t>Orientačná cena</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>neuvádzame — VESMA prepočítava kg na kWh</t>
+          <t>10 000 – 40 000 EUR podľa výkonu a riešenia skladu paliva</t>
         </is>
       </c>
       <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>VESMA prepočítava zadané kg paliva na kWh. Ak máte hodnotu, ktorú považujete za správnu, prosíme ju sem.</t>
-        </is>
-      </c>
+      <c r="D14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Výhrevnosť štiepky</t>
+          <t>Návratnosť</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>neuvádzame — závisí od vlhkosti</t>
+          <t>7 – 15 rokov</t>
         </is>
       </c>
       <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Ak hodnota závisí od vlhkosti, uveďte prosím pri akej.</t>
-        </is>
-      </c>
+      <c r="D15" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>PRE POROVNANIE — iné opatrenia v katalógu</t>
+          <t>VÝHREVNOSTI PALÍV — hodnoty, ktoré sú dnes napevno v kóde</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Opatrenie</t>
+          <t>Palivo</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Orientačná cena</t>
+          <t>V aplikácii teraz [kWh/kg]</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Návratnosť</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr"/>
+          <t>Potvrdená hodnota [kWh/kg]</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Tepelné čerpadlo vzduch/voda</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>8 000 – 18 000 EUR</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>8 – 15 rokov</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr"/>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>(vzor) Brikety</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>neevidujeme</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>pridať / netreba</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Zateplenie fasády (ETICS)</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>50 – 100 EUR/m² fasády</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>8 – 15 rokov</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr"/>
+          <t>Pelety</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>Štiepka</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Závisí od vlhkosti — ak jedna hodnota nestačí, uveďte prosím pri akej vlhkosti platí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Uhlie</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Drevo</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Drevo s vlhkosťou 20 % a 50 % sa líši takmer dvojnásobne. Je jedna hodnota obhájiteľná, alebo sa treba pýtať aj na vlhkosť?</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Ak si myslíte, že výhrevnosť má zadávať používateľ a nie byť napevno v kóde, napíšte to sem — je to zmena dotazníka, nie len čísla:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>PRE POROVNANIE — iné opatrenia v katalógu</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Opatrenie</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Orientačná cena</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Návratnosť</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Tepelné čerpadlo vzduch/voda</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>8 000 – 18 000 EUR</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>8 – 15 rokov</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Zateplenie fasády (ETICS)</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>50 – 100 EUR/m² fasády</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>8 – 15 rokov</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
           <t>Batériové úložisko</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>4 000 – 10 000 EUR (5–10 kWh)</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>8 – 12 rokov</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr"/>
+      <c r="D33" s="11" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A27:D27"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1838,67 +1989,67 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>4. Hustota inštalovaného príkonu osvetlenia [W/m²]</t>
+          <t>4. Hustota inštalovaného príkonu osvetlenia [W/m²]  [E4]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Načo to je: keď používateľ pozná počet svietidiel, VESMA počíta z neho. Keď ho nepozná,</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>odhaduje príkon z plochy pomocou tejto tabuľky. Tabuľka zároveň prepočítava kusy na watty,</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>takže ovplyvňuje váhu celého parametra osvetlenia v porovnaní areálov (hárok 2).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Prečo to nevieme dohľadať: oficiálna prepočtová tabuľka „plocha → W" v slovenskej legislatíve</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>neexistuje. Vyhláška č. 541/2007 Z. z. a STN EN 12464-1 predpisujú osvetlenosť v luxoch, nie</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>inštalovaný príkon. Vyhláška č. 364/2012 Z. z. počíta príkon metódou LENI podľa STN EN 15193</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>z konkrétnych svietidiel a prevádzkových časov — čo laik pri obhliadke nemá.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
+      <c r="A10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Hodnoty nižšie sú orientačné pásma z bežnej projekčnej praxe pri LED.</t>
         </is>
@@ -2115,67 +2266,67 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5. Dennostupne podľa okresu (klimatická normalizácia, STN 73 0550)</t>
+          <t>5. Dennostupne podľa okresu (klimatická normalizácia, STN 73 0550)  [E5]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Načo to je: bez klimatickej normalizácie sa nedá poctivo porovnať spotreba budovy v Poprade</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>so spotrebou v Komárne, ani spotreba tej istej budovy v studenej a v miernej zime.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Dennostupňová metóda podľa STN 73 0550 to rieši — potrebujeme k nej dennostupne podľa lokality.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Toto nie je otázka odhadu, ale zdroja dát. Ak viete, odkiaľ tieto hodnoty vziať (SHMÚ, iná</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>databáza, vlastný zdroj), stačí nám povedať zdroj — tabuľku doplníme sami. Vyplňte ju len</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>vtedy, ak máte hodnoty poruke.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
+      <c r="A9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Ak sa dennostupne bežne uvádzajú za kraj alebo klimatickú oblasť a nie za okres, napíšte to</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>do poznámky pod tabuľkou — prispôsobíme tomu dátový model.</t>
         </is>
@@ -3120,7 +3271,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr"/>
+      <c r="A94" s="6" t="inlineStr"/>
       <c r="B94" s="15" t="n"/>
       <c r="C94" s="15" t="n"/>
       <c r="D94" s="15" t="n"/>
